--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2019,22 +2019,62 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>21/02/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M28" t="n">
+        <v>12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2077,22 +2077,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ceuta</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2135,22 +2135,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M30" t="n">
+        <v>12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>14</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2193,22 +2193,62 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M31" t="n">
+        <v>22</v>
+      </c>
+      <c r="N31" t="n">
+        <v>9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2251,22 +2251,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>22/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M32" t="n">
+        <v>15</v>
+      </c>
+      <c r="N32" t="n">
+        <v>14</v>
+      </c>
+      <c r="O32" t="n">
+        <v>7</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2309,22 +2309,62 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M33" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" t="n">
+        <v>20</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2367,40 +2367,120 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>13</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M35" t="n">
+        <v>15</v>
+      </c>
+      <c r="N35" t="n">
+        <v>26</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2483,22 +2483,62 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="N36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O36" t="n">
+        <v>7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2541,22 +2541,62 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>La Coruna</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M37" t="n">
+        <v>12</v>
+      </c>
+      <c r="N37" t="n">
+        <v>12</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2599,22 +2599,62 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" t="n">
+        <v>7</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2657,22 +2657,62 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M39" t="n">
+        <v>12</v>
+      </c>
+      <c r="N39" t="n">
+        <v>9</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2715,22 +2715,62 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M40" t="n">
+        <v>19</v>
+      </c>
+      <c r="N40" t="n">
+        <v>8</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2773,22 +2773,62 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Real Sociedad B</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>17</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2831,22 +2831,62 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M42" t="n">
+        <v>18</v>
+      </c>
+      <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="n">
+        <v>8</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>

--- a/new-stats/cd-mirandes.xlsx
+++ b/new-stats/cd-mirandes.xlsx
@@ -2889,22 +2889,62 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>5</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
